--- a/diseases/d164/2026-2029.xlsx
+++ b/diseases/d164/2026-2029.xlsx
@@ -5686,6 +5686,151 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>D164</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>hantavirus-pulmonary-syndrome</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>D164</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>汉他病毒肺症候群</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP36" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS36" t="inlineStr"/>
+      <c r="AT36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV36" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA36" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB36" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC36" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5719,7 +5864,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -5802,7 +5947,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10">
@@ -5812,7 +5957,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d164/2026-2029.xlsx
+++ b/diseases/d164/2026-2029.xlsx
@@ -5831,6 +5831,151 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>D164</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>hantavirus-pulmonary-syndrome</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>D164</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>汉他病毒肺症候群</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP37" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS37" t="inlineStr"/>
+      <c r="AT37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV37" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA37" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB37" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC37" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5864,7 +6009,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -5947,7 +6092,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10">
@@ -5957,7 +6102,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d164/2026-2029.xlsx
+++ b/diseases/d164/2026-2029.xlsx
@@ -5976,6 +5976,151 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>D164</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>hantavirus-pulmonary-syndrome</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>D164</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>汉他病毒肺症候群</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP38" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS38" t="inlineStr"/>
+      <c r="AT38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV38" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA38" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB38" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC38" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6009,7 +6154,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -6092,7 +6237,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10">
@@ -6102,7 +6247,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d164/2026-2029.xlsx
+++ b/diseases/d164/2026-2029.xlsx
@@ -6121,6 +6121,151 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>D164</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>hantavirus-pulmonary-syndrome</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>D164</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>汉他病毒肺症候群</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP39" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR39" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS39" t="inlineStr"/>
+      <c r="AT39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV39" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA39" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB39" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC39" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6154,7 +6299,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -6237,7 +6382,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10">
@@ -6247,7 +6392,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d164/2026-2029.xlsx
+++ b/diseases/d164/2026-2029.xlsx
@@ -6266,6 +6266,151 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>D164</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>hantavirus-pulmonary-syndrome</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>D164</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>汉他病毒肺症候群</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP40" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR40" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS40" t="inlineStr"/>
+      <c r="AT40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV40" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA40" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB40" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC40" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6299,7 +6444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -6382,7 +6527,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10">
@@ -6392,7 +6537,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d164/2026-2029.xlsx
+++ b/diseases/d164/2026-2029.xlsx
@@ -6411,6 +6411,151 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>D164</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>hantavirus-pulmonary-syndrome</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>D164</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>汉他病毒肺症候群</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP41" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR41" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS41" t="inlineStr"/>
+      <c r="AT41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV41" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA41" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB41" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC41" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6444,7 +6589,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -6527,7 +6672,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10">
@@ -6537,7 +6682,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d164/2026-2029.xlsx
+++ b/diseases/d164/2026-2029.xlsx
@@ -2201,12 +2201,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -2240,84 +2240,93 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>HOLD_US_b702f329f03a151013e28408b2cc; HOLD_US_c0089eee13c9334f1168e05603af</t>
+        </is>
+      </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -2344,17 +2353,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2379,7 +2388,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -2388,84 +2397,168 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>HOLD_US_c0089eee13c9334f1168e05603af</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN13" t="b">
+        <v>1</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS13" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>HOLD_US_b702f329f03a151013e28408b2cc; HOLD_US_c0089eee13c9334f1168e05603af</t>
+        </is>
+      </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -2497,12 +2590,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US-NY</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>New York, United States</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2527,68 +2620,79 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>HOLD_US_c0089eee13c9334f1168e05603af</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS14" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>HOLD_US_c0089eee13c9334f1168e05603af</t>
+        </is>
+      </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2598,17 +2702,17 @@
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
@@ -2640,17 +2744,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US-NY</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>New York, United States</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2675,68 +2779,152 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>HOLD_US_c0089eee13c9334f1168e05603af</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>country:US-NY:national</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN15" t="b">
+        <v>1</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS15" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>HOLD_US_c0089eee13c9334f1168e05603af</t>
+        </is>
+      </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2746,17 +2934,17 @@
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
@@ -2823,12 +3011,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N16" t="n">
@@ -2971,12 +3159,12 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N17" t="n">
@@ -3119,12 +3307,12 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="N18" t="n">
@@ -3267,12 +3455,12 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="N19" t="n">
@@ -3415,12 +3603,12 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="N20" t="n">
@@ -3563,12 +3751,12 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="N21" t="n">
@@ -3711,7 +3899,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -3859,18 +4047,21 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N23" t="n">
         <v>0</v>
       </c>
       <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
@@ -4004,18 +4195,21 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N24" t="n">
         <v>0</v>
       </c>
       <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
@@ -4149,18 +4343,21 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N25" t="n">
         <v>0</v>
       </c>
       <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
         <v>0</v>
       </c>
       <c r="R25" t="n">
@@ -4294,18 +4491,21 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N26" t="n">
         <v>0</v>
       </c>
       <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
         <v>0</v>
       </c>
       <c r="R26" t="n">
@@ -4439,12 +4639,12 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N27" t="n">
@@ -4584,12 +4784,12 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N28" t="n">
@@ -4729,12 +4929,12 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N29" t="n">
@@ -4874,12 +5074,12 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N30" t="n">
@@ -5019,7 +5219,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -5164,12 +5364,12 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N32" t="n">
@@ -5309,12 +5509,12 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N33" t="n">
@@ -5454,12 +5654,12 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N34" t="n">
@@ -5599,12 +5799,12 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N35" t="n">
@@ -5744,7 +5944,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -5889,12 +6089,12 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N37" t="n">
@@ -6034,12 +6234,12 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N38" t="n">
@@ -6179,12 +6379,12 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N39" t="n">
@@ -6324,12 +6524,12 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N40" t="n">
@@ -6469,12 +6669,12 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N41" t="n">
@@ -6551,6 +6751,1366 @@
         </is>
       </c>
       <c r="BC41" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>D164</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>hantavirus-pulmonary-syndrome</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>D164</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>汉他病毒肺症候群</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>1</v>
+      </c>
+      <c r="O42" t="n">
+        <v>1</v>
+      </c>
+      <c r="P42" t="n">
+        <v>1</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP42" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ42" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS42" t="inlineStr">
+        <is>
+          <t>HOLD_US_b702f329f03a151013e28408b2cc; HOLD_US_c0089eee13c9334f1168e05603af</t>
+        </is>
+      </c>
+      <c r="AT42" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV42" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA42" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB42" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC42" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>D164</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>hantavirus-pulmonary-syndrome</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>D164</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>汉他病毒肺症候群</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>1</v>
+      </c>
+      <c r="O43" t="n">
+        <v>1</v>
+      </c>
+      <c r="P43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>HOLD_US_c0089eee13c9334f1168e05603af</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN43" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP43" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ43" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS43" t="inlineStr">
+        <is>
+          <t>HOLD_US_b702f329f03a151013e28408b2cc; HOLD_US_c0089eee13c9334f1168e05603af</t>
+        </is>
+      </c>
+      <c r="AT43" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV43" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA43" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB43" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC43" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>D164</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>hantavirus-pulmonary-syndrome</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>US-MD</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Maryland, United States</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>D164</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>汉他病毒肺症候群</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N44" t="n">
+        <v>1</v>
+      </c>
+      <c r="O44" t="n">
+        <v>1</v>
+      </c>
+      <c r="P44" t="n">
+        <v>1</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>HOLD_US_c0089eee13c9334f1168e05603af</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP44" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ44" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS44" t="inlineStr">
+        <is>
+          <t>HOLD_US_c0089eee13c9334f1168e05603af</t>
+        </is>
+      </c>
+      <c r="AT44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV44" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="BA44" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="BB44" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+        </is>
+      </c>
+      <c r="BC44" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>D164</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>hantavirus-pulmonary-syndrome</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>US-MD</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Maryland, United States</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>D164</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>汉他病毒肺症候群</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>1</v>
+      </c>
+      <c r="O45" t="n">
+        <v>1</v>
+      </c>
+      <c r="P45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>HOLD_US_c0089eee13c9334f1168e05603af</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>country:US-MD:national</t>
+        </is>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN45" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP45" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ45" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS45" t="inlineStr">
+        <is>
+          <t>HOLD_US_c0089eee13c9334f1168e05603af</t>
+        </is>
+      </c>
+      <c r="AT45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV45" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="BA45" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="BB45" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+        </is>
+      </c>
+      <c r="BC45" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>D164</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>hantavirus-pulmonary-syndrome</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>D164</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>汉他病毒肺症候群</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP46" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS46" t="inlineStr"/>
+      <c r="AT46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV46" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA46" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB46" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC46" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>D164</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>hantavirus-pulmonary-syndrome</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>D164</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>汉他病毒肺症候群</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP47" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS47" t="inlineStr"/>
+      <c r="AT47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV47" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA47" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB47" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC47" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>D164</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>hantavirus-pulmonary-syndrome</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>D164</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>汉他病毒肺症候群</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP48" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS48" t="inlineStr"/>
+      <c r="AT48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV48" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA48" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB48" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC48" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>D164</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>hantavirus-pulmonary-syndrome</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>D164</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Hantavirus pulmonary syndrome</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>汉他病毒肺症候群</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP49" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS49" t="inlineStr"/>
+      <c r="AT49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV49" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA49" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB49" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC49" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -6672,7 +8232,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10">
@@ -6682,7 +8242,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11">
@@ -6702,7 +8262,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -6712,7 +8272,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -6734,7 +8294,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
